--- a/diseases/d049/2026-2029.xlsx
+++ b/diseases/d049/2026-2029.xlsx
@@ -22491,12 +22491,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -22521,12 +22521,12 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N126" t="n">
@@ -22569,40 +22569,185 @@
       </c>
       <c r="AV126" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr"/>
+      <c r="AT127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW126" t="inlineStr">
+      <c r="AW127" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX126" t="inlineStr">
+      <c r="AX127" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY126" t="inlineStr">
+      <c r="AY127" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ126" t="inlineStr">
+      <c r="AZ127" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA126" t="inlineStr">
+      <c r="BA127" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB126" t="inlineStr">
+      <c r="BB127" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC126" t="inlineStr">
+      <c r="BC127" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -22724,7 +22869,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10">
@@ -22734,7 +22879,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d049/2026-2029.xlsx
+++ b/diseases/d049/2026-2029.xlsx
@@ -20170,12 +20170,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -20212,6 +20212,9 @@
         <v>0</v>
       </c>
       <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
@@ -20248,42 +20251,42 @@
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -20315,12 +20318,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -20345,7 +20348,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -20393,42 +20396,42 @@
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -20460,12 +20463,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -20504,9 +20507,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="P115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -20515,82 +20515,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ115" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20617,7 +20603,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -20669,98 +20655,23 @@
       <c r="P116" t="n">
         <v>0</v>
       </c>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U116" t="inlineStr">
         <is>
           <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
         </is>
       </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="W116" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X116" t="inlineStr">
-        <is>
-          <t>Middle East Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD116" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE116" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF116" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG116" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN116" t="b">
-        <v>1</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -20854,17 +20765,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -20889,7 +20800,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -20903,76 +20814,168 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="R117" t="n">
-        <v>0</v>
-      </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN117" t="b">
+        <v>1</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS117" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
       <c r="AT117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -21004,12 +21007,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -21048,9 +21051,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="P118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -21059,82 +21059,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="AA118" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21161,7 +21147,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -21213,98 +21199,23 @@
       <c r="P119" t="n">
         <v>0</v>
       </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U119" t="inlineStr">
         <is>
           <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
         </is>
       </c>
-      <c r="V119" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="W119" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X119" t="inlineStr">
-        <is>
-          <t>Middle East Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y119" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD119" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE119" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF119" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG119" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN119" t="b">
-        <v>1</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -21398,17 +21309,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -21433,7 +21344,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -21447,76 +21358,168 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="R120" t="n">
-        <v>0</v>
-      </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN120" t="b">
+        <v>1</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -21548,12 +21551,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -21592,9 +21595,6 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="P121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
@@ -21603,82 +21603,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ121" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21705,7 +21691,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -21757,98 +21743,23 @@
       <c r="P122" t="n">
         <v>0</v>
       </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U122" t="inlineStr">
         <is>
           <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
         </is>
       </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="W122" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>Middle East Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD122" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE122" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF122" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG122" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN122" t="b">
-        <v>1</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -21942,17 +21853,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -21977,7 +21888,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -21991,76 +21902,168 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="R123" t="n">
-        <v>0</v>
-      </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN123" t="b">
+        <v>1</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
       <c r="AT123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -22092,12 +22095,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -22136,9 +22139,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="P124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -22147,82 +22147,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ124" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22249,7 +22235,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -22301,98 +22287,23 @@
       <c r="P125" t="n">
         <v>0</v>
       </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U125" t="inlineStr">
         <is>
           <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
         </is>
       </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X125" t="inlineStr">
-        <is>
-          <t>Middle East Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD125" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE125" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF125" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG125" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN125" t="b">
-        <v>1</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -22486,17 +22397,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -22521,7 +22432,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -22535,76 +22446,168 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
-      <c r="R126" t="n">
-        <v>0</v>
-      </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN126" t="b">
+        <v>1</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
       <c r="AT126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -22636,12 +22639,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -22666,12 +22669,12 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N127" t="n">
@@ -22714,40 +22717,584 @@
       </c>
       <c r="AV127" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AT128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN129" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AT129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr"/>
+      <c r="AT130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW127" t="inlineStr">
+      <c r="AW130" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX127" t="inlineStr">
+      <c r="AX130" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY127" t="inlineStr">
+      <c r="AY130" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ127" t="inlineStr">
+      <c r="AZ130" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA127" t="inlineStr">
+      <c r="BA130" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB127" t="inlineStr">
+      <c r="BB130" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC127" t="inlineStr">
+      <c r="BC130" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -22869,7 +23416,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10">
@@ -22879,7 +23426,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11">
@@ -22899,7 +23446,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d049/2026-2029.xlsx
+++ b/diseases/d049/2026-2029.xlsx
@@ -23300,6 +23300,151 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr"/>
+      <c r="AT131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23333,7 +23478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -23416,7 +23561,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10">
@@ -23426,7 +23571,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d049/2026-2029.xlsx
+++ b/diseases/d049/2026-2029.xlsx
@@ -23445,6 +23445,405 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP132" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AT132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV132" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA132" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB132" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC132" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM133" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN133" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP133" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AT133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV133" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA133" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB133" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC133" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23561,7 +23960,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10">
@@ -23571,7 +23970,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11">
@@ -23591,7 +23990,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d049/2026-2029.xlsx
+++ b/diseases/d049/2026-2029.xlsx
@@ -20318,12 +20318,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -20396,42 +20396,42 @@
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -20493,7 +20493,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -20541,42 +20541,42 @@
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -20608,12 +20608,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -20652,9 +20652,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="P116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -20663,82 +20660,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="AA116" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ116" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20765,7 +20748,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -20817,98 +20800,23 @@
       <c r="P117" t="n">
         <v>0</v>
       </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U117" t="inlineStr">
         <is>
           <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
         </is>
       </c>
-      <c r="V117" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="W117" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X117" t="inlineStr">
-        <is>
-          <t>Middle East Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y117" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD117" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE117" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF117" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG117" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN117" t="b">
-        <v>1</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -21002,17 +20910,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -21037,7 +20945,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -21051,76 +20959,168 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="R118" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN118" t="b">
+        <v>1</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
       <c r="AT118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -21152,12 +21152,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -21196,9 +21196,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="P119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -21207,82 +21204,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21309,7 +21292,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -21361,98 +21344,23 @@
       <c r="P120" t="n">
         <v>0</v>
       </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U120" t="inlineStr">
         <is>
           <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
         </is>
       </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X120" t="inlineStr">
-        <is>
-          <t>Middle East Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD120" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE120" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF120" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG120" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN120" t="b">
-        <v>1</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -21546,17 +21454,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -21581,7 +21489,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -21595,76 +21503,168 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN121" t="b">
+        <v>1</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -21696,12 +21696,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -21740,9 +21740,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="P122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -21751,82 +21748,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="AA122" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ122" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21853,7 +21836,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -21905,98 +21888,23 @@
       <c r="P123" t="n">
         <v>0</v>
       </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U123" t="inlineStr">
         <is>
           <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
         </is>
       </c>
-      <c r="V123" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="W123" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X123" t="inlineStr">
-        <is>
-          <t>Middle East Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD123" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE123" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF123" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG123" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN123" t="b">
-        <v>1</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -22090,17 +21998,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -22125,7 +22033,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -22139,76 +22047,168 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="R124" t="n">
-        <v>0</v>
-      </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN124" t="b">
+        <v>1</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
       <c r="AT124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -22240,12 +22240,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -22284,9 +22284,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="P125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -22295,82 +22292,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22397,7 +22380,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -22449,98 +22432,23 @@
       <c r="P126" t="n">
         <v>0</v>
       </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U126" t="inlineStr">
         <is>
           <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
         </is>
       </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>Middle East Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD126" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE126" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF126" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG126" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN126" t="b">
-        <v>1</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -22634,17 +22542,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -22669,7 +22577,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -22683,76 +22591,168 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="R127" t="n">
-        <v>0</v>
-      </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN127" t="b">
+        <v>1</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
       <c r="AT127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -22784,12 +22784,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -22828,9 +22828,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="P128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -22839,82 +22836,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="AA128" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ128" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS128" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22941,7 +22924,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -22993,98 +22976,23 @@
       <c r="P129" t="n">
         <v>0</v>
       </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U129" t="inlineStr">
         <is>
           <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
         </is>
       </c>
-      <c r="V129" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="W129" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X129" t="inlineStr">
-        <is>
-          <t>Middle East Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y129" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD129" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE129" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF129" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG129" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ129" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN129" t="b">
-        <v>1</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -23178,17 +23086,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -23213,12 +23121,12 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N130" t="n">
@@ -23227,76 +23135,168 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="R130" t="n">
-        <v>0</v>
-      </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN130" t="b">
+        <v>1</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
       <c r="AT130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -23328,12 +23328,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -23358,7 +23358,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -23406,42 +23406,42 @@
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -23473,12 +23473,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -23517,9 +23517,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="P132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -23528,82 +23525,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="AA132" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ132" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr"/>
       <c r="AT132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23630,7 +23613,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -23682,98 +23665,23 @@
       <c r="P133" t="n">
         <v>0</v>
       </c>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U133" t="inlineStr">
         <is>
           <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
         </is>
       </c>
-      <c r="V133" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="W133" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X133" t="inlineStr">
-        <is>
-          <t>Middle East Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y133" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD133" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE133" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF133" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG133" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ133" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK133" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN133" t="b">
-        <v>1</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -23839,6 +23747,787 @@
         </is>
       </c>
       <c r="BC133" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM134" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN134" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AT134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV134" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA134" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB134" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC134" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr"/>
+      <c r="AT135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV135" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA135" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB135" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC135" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP136" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AT136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV136" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA136" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB136" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC136" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN137" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP137" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AT137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV137" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA137" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB137" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC137" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -23877,7 +24566,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -23960,7 +24649,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
@@ -23970,7 +24659,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -23990,7 +24679,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d049/2026-2029.xlsx
+++ b/diseases/d049/2026-2029.xlsx
@@ -14945,12 +14945,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -14989,76 +14989,87 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="R83" t="n">
-        <v>0</v>
-      </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_MERS</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS83" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_MERS</t>
+        </is>
+      </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -15085,17 +15096,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -15134,76 +15145,165 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="R84" t="n">
-        <v>0</v>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_MERS</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_MERS</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征（MERS）</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Official provincial report count for MERS-CoV disease; source month is retained and absent rows remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN84" t="b">
+        <v>1</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_MERS</t>
+        </is>
+      </c>
       <c r="AT84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -15235,12 +15335,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -15265,7 +15365,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -15313,42 +15413,42 @@
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -15380,12 +15480,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -15410,7 +15510,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -15424,9 +15524,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="P86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -15435,82 +15532,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ86" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS86" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -15537,17 +15620,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -15572,7 +15655,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -15586,168 +15669,76 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="P87" t="n">
-        <v>0</v>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>Middle East Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD87" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE87" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF87" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG87" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN87" t="b">
-        <v>1</v>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ87" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS87" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15779,12 +15770,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -15809,7 +15800,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -15823,6 +15814,9 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -15831,68 +15825,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -15919,7 +15927,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -15954,7 +15962,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -15971,23 +15979,98 @@
       <c r="P89" t="n">
         <v>0</v>
       </c>
-      <c r="R89" t="n">
-        <v>0</v>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U89" t="inlineStr">
         <is>
           <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
         </is>
       </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN89" t="b">
+        <v>1</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -16081,17 +16164,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -16116,7 +16199,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -16130,168 +16213,76 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>Middle East Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD90" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE90" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF90" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG90" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN90" t="b">
-        <v>1</v>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ90" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16323,12 +16314,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -16353,7 +16344,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -16367,6 +16358,9 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -16375,68 +16369,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
       <c r="AT91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -16463,7 +16471,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -16498,7 +16506,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -16515,23 +16523,98 @@
       <c r="P92" t="n">
         <v>0</v>
       </c>
-      <c r="R92" t="n">
-        <v>0</v>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U92" t="inlineStr">
         <is>
           <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
         </is>
       </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN92" t="b">
+        <v>1</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -16625,17 +16708,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -16660,7 +16743,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -16674,168 +16757,76 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="P93" t="n">
-        <v>0</v>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X93" t="inlineStr">
-        <is>
-          <t>Middle East Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD93" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE93" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF93" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG93" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN93" t="b">
-        <v>1</v>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ93" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16867,12 +16858,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -16897,7 +16888,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -16911,6 +16902,9 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -16919,68 +16913,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
       <c r="AT94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -17007,7 +17015,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -17042,7 +17050,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -17059,23 +17067,98 @@
       <c r="P95" t="n">
         <v>0</v>
       </c>
-      <c r="R95" t="n">
-        <v>0</v>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U95" t="inlineStr">
         <is>
           <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
         </is>
       </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN95" t="b">
+        <v>1</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -17169,17 +17252,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -17204,7 +17287,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -17218,168 +17301,76 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="P96" t="n">
-        <v>0</v>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>Middle East Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD96" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE96" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF96" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG96" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN96" t="b">
-        <v>1</v>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ96" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -17411,12 +17402,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -17441,12 +17432,12 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N97" t="n">
@@ -17455,7 +17446,7 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
+      <c r="P97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">
@@ -17466,68 +17457,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS97" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
       <c r="AT97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -17554,17 +17559,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -17589,12 +17594,12 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N98" t="n">
@@ -17603,76 +17608,168 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="R98" t="n">
-        <v>0</v>
-      </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN98" t="b">
+        <v>1</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
       <c r="AT98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -17704,12 +17801,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -17746,6 +17843,9 @@
         <v>0</v>
       </c>
       <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
@@ -17782,42 +17882,42 @@
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -17849,12 +17949,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -17879,7 +17979,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -17893,76 +17993,87 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="R100" t="n">
-        <v>0</v>
-      </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_MERS</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS100" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_MERS</t>
+        </is>
+      </c>
       <c r="AT100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -17989,17 +18100,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -18024,7 +18135,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -18038,26 +18149,98 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="P101" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" t="n">
-        <v>0</v>
-      </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+          <t>SER_CN_PROV_REPORT_MERS</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_MERS</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征（MERS）</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>country:CN-FJ:national</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Official provincial report count for MERS-CoV disease; source month is retained and absent rows remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN101" t="b">
+        <v>1</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -18076,7 +18259,7 @@
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+          <t>SER_CN_PROV_REPORT_MERS</t>
         </is>
       </c>
       <c r="AT101" t="n">
@@ -18089,42 +18272,42 @@
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -18151,17 +18334,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -18186,7 +18369,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -18200,101 +18383,20 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="P102" t="n">
-        <v>0</v>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="W102" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>Middle East Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>SER_CN_PROV_REPORT_MERS</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD102" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE102" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF102" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG102" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN102" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -18313,7 +18415,7 @@
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+          <t>SER_CN_PROV_REPORT_MERS</t>
         </is>
       </c>
       <c r="AT102" t="n">
@@ -18326,42 +18428,42 @@
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -18388,17 +18490,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -18423,7 +18525,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -18437,76 +18539,165 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="R103" t="n">
-        <v>0</v>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_MERS</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_MERS</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征（MERS）</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Official provincial report count for MERS-CoV disease; source month is retained and absent rows remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN103" t="b">
+        <v>1</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_MERS</t>
+        </is>
+      </c>
       <c r="AT103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -18538,12 +18729,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -18568,7 +18759,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -18582,9 +18773,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="P104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -18593,82 +18781,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="AA104" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ104" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -18695,17 +18869,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -18730,7 +18904,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -18744,168 +18918,76 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="P105" t="n">
-        <v>0</v>
-      </c>
-      <c r="U105" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="V105" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="W105" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t>Middle East Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA105" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD105" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE105" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF105" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG105" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN105" t="b">
-        <v>1</v>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ105" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -18967,7 +19049,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -19112,7 +19194,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -19274,7 +19356,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -19511,7 +19593,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -19626,12 +19708,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -19656,7 +19738,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -19670,6 +19752,9 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -19678,68 +19763,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
       <c r="AT110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -19766,7 +19865,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -19801,7 +19900,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -19818,23 +19917,98 @@
       <c r="P111" t="n">
         <v>0</v>
       </c>
-      <c r="R111" t="n">
-        <v>0</v>
-      </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U111" t="inlineStr">
         <is>
           <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
         </is>
       </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN111" t="b">
+        <v>1</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -19928,17 +20102,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -19963,7 +20137,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -19977,168 +20151,76 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="P112" t="n">
-        <v>0</v>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>Middle East Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA112" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD112" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE112" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF112" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG112" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN112" t="b">
-        <v>1</v>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ112" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20170,12 +20252,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -20200,12 +20282,12 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N113" t="n">
@@ -20214,7 +20296,7 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
+      <c r="P113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
@@ -20225,68 +20307,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
       <c r="AT113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -20313,17 +20409,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -20348,12 +20444,12 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N114" t="n">
@@ -20362,76 +20458,168 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="R114" t="n">
-        <v>0</v>
-      </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN114" t="b">
+        <v>1</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS114" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
       <c r="AT114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -20463,12 +20651,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -20493,12 +20681,12 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N115" t="n">
@@ -20541,42 +20729,42 @@
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20638,12 +20826,12 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N116" t="n">
@@ -20783,12 +20971,12 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N117" t="n">
@@ -20945,12 +21133,12 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N118" t="n">
@@ -21152,12 +21340,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -21182,7 +21370,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -21194,6 +21382,9 @@
         <v>0</v>
       </c>
       <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
@@ -21230,17 +21421,17 @@
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -21250,22 +21441,22 @@
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -21297,12 +21488,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -21327,7 +21518,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -21341,25 +21532,19 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="P120" t="n">
-        <v>0</v>
-      </c>
-      <c r="R120" t="n">
-        <v>0</v>
-      </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+          <t>SER_CN_PROV_REPORT_MERS</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -21379,7 +21564,7 @@
       </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+          <t>SER_CN_PROV_REPORT_MERS</t>
         </is>
       </c>
       <c r="AT120" t="n">
@@ -21392,42 +21577,42 @@
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -21459,12 +21644,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -21489,7 +21674,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -21503,27 +21688,24 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="P121" t="n">
-        <v>0</v>
-      </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+          <t>SER_CN_PROV_REPORT_MERS</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+          <t>SER_CN_PROV_REPORT_MERS</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>Middle East Respiratory Syndrome</t>
+          <t>中东呼吸综合征（MERS）</t>
         </is>
       </c>
       <c r="Y121" t="inlineStr">
@@ -21533,12 +21715,12 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
@@ -21548,7 +21730,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD121" t="inlineStr">
@@ -21583,17 +21765,17 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Official provincial report count for MERS-CoV disease; source month is retained and absent rows remain unknown.</t>
         </is>
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -21616,7 +21798,7 @@
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+          <t>SER_CN_PROV_REPORT_MERS</t>
         </is>
       </c>
       <c r="AT121" t="n">
@@ -21629,42 +21811,42 @@
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -21696,12 +21878,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -21726,7 +21908,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -21774,42 +21956,42 @@
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -21841,12 +22023,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -21871,7 +22053,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -21885,9 +22067,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="P123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -21896,82 +22075,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ123" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -21998,17 +22163,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -22033,7 +22198,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -22047,168 +22212,76 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="P124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="W124" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X124" t="inlineStr">
-        <is>
-          <t>Middle East Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD124" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE124" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF124" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG124" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN124" t="b">
-        <v>1</v>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ124" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22240,12 +22313,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -22270,7 +22343,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -22284,6 +22357,9 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -22292,68 +22368,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
       <c r="AT125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -22380,7 +22470,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -22415,7 +22505,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -22432,23 +22522,98 @@
       <c r="P126" t="n">
         <v>0</v>
       </c>
-      <c r="R126" t="n">
-        <v>0</v>
-      </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U126" t="inlineStr">
         <is>
           <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
         </is>
       </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN126" t="b">
+        <v>1</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -22542,17 +22707,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -22577,7 +22742,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -22591,168 +22756,76 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="P127" t="n">
-        <v>0</v>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="W127" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X127" t="inlineStr">
-        <is>
-          <t>Middle East Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD127" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE127" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF127" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG127" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN127" t="b">
-        <v>1</v>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ127" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22784,12 +22857,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -22814,7 +22887,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -22828,6 +22901,9 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -22836,68 +22912,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS128" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
       <c r="AT128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -22924,7 +23014,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -22959,7 +23049,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -22976,23 +23066,98 @@
       <c r="P129" t="n">
         <v>0</v>
       </c>
-      <c r="R129" t="n">
-        <v>0</v>
-      </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U129" t="inlineStr">
         <is>
           <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
         </is>
       </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN129" t="b">
+        <v>1</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -23086,17 +23251,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -23121,7 +23286,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -23135,168 +23300,76 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="P130" t="n">
-        <v>0</v>
-      </c>
-      <c r="U130" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="V130" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="W130" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X130" t="inlineStr">
-        <is>
-          <t>Middle East Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y130" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA130" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD130" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE130" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF130" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG130" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI130" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN130" t="b">
-        <v>1</v>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ130" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr"/>
       <c r="AT130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23328,12 +23401,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -23358,12 +23431,12 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N131" t="n">
@@ -23372,6 +23445,9 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -23380,68 +23456,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
       <c r="AT131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -23468,17 +23558,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -23503,12 +23593,12 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N132" t="n">
@@ -23517,76 +23607,168 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="R132" t="n">
-        <v>0</v>
-      </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN132" t="b">
+        <v>1</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
       <c r="AT132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -23618,12 +23800,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -23648,12 +23830,12 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N133" t="n">
@@ -23662,9 +23844,6 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="P133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
@@ -23673,82 +23852,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ133" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23775,7 +23940,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -23810,12 +23975,12 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N134" t="n">
@@ -23827,98 +23992,23 @@
       <c r="P134" t="n">
         <v>0</v>
       </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U134" t="inlineStr">
         <is>
           <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
         </is>
       </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="W134" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X134" t="inlineStr">
-        <is>
-          <t>Middle East Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD134" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE134" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF134" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG134" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN134" t="b">
-        <v>1</v>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
@@ -24012,17 +24102,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -24047,12 +24137,12 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N135" t="n">
@@ -24061,76 +24151,168 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="R135" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN135" t="b">
+        <v>1</v>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
       <c r="AT135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -24162,12 +24344,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -24192,12 +24374,12 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N136" t="n">
@@ -24206,9 +24388,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="P136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -24217,82 +24396,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="AA136" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ136" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24319,7 +24484,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -24354,12 +24519,12 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N137" t="n">
@@ -24371,98 +24536,23 @@
       <c r="P137" t="n">
         <v>0</v>
       </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U137" t="inlineStr">
         <is>
           <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
         </is>
       </c>
-      <c r="V137" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
-        </is>
-      </c>
-      <c r="W137" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X137" t="inlineStr">
-        <is>
-          <t>Middle East Respiratory Syndrome</t>
-        </is>
-      </c>
-      <c r="Y137" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD137" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE137" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF137" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG137" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN137" t="b">
-        <v>1</v>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
@@ -24528,6 +24618,1476 @@
         </is>
       </c>
       <c r="BC137" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD138" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM138" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN138" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP138" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AT138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV138" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA138" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB138" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC138" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP139" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr"/>
+      <c r="AT139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV139" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA139" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB139" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC139" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP140" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr"/>
+      <c r="AT140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV140" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA140" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB140" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC140" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP141" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AT141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV141" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA141" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB141" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC141" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN142" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AT142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA142" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB142" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC142" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr"/>
+      <c r="AT143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AT144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA144" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC144" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN145" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP145" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AT145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV145" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA145" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC145" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -24649,7 +26209,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10">
@@ -24659,7 +26219,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -24679,7 +26239,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -24689,7 +26249,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d049/2026-2029.xlsx
+++ b/diseases/d049/2026-2029.xlsx
@@ -26093,6 +26093,695 @@
         </is>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr"/>
+      <c r="AT146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV146" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA146" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC146" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
+      <c r="R147" t="n">
+        <v>0</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP147" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AT147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV147" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA147" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB147" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC147" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" t="n">
+        <v>0</v>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN148" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP148" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AT148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV148" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA148" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB148" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC148" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr"/>
+      <c r="AT149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV149" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA149" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC149" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26126,7 +26815,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -26209,7 +26898,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10">
@@ -26219,7 +26908,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -26239,7 +26928,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d049/2026-2029.xlsx
+++ b/diseases/d049/2026-2029.xlsx
@@ -26665,12 +26665,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -26695,12 +26695,12 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N149" t="n">
@@ -26743,40 +26743,185 @@
       </c>
       <c r="AV149" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA149" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC149" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr"/>
+      <c r="AT150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW149" t="inlineStr">
+      <c r="AW150" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX149" t="inlineStr">
+      <c r="AX150" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY149" t="inlineStr">
+      <c r="AY150" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ149" t="inlineStr">
+      <c r="AZ150" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA149" t="inlineStr">
+      <c r="BA150" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB149" t="inlineStr">
+      <c r="BB150" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC149" t="inlineStr">
+      <c r="BC150" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -26898,7 +27043,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10">
@@ -26908,7 +27053,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d049/2026-2029.xlsx
+++ b/diseases/d049/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3402,6 +3417,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3547,6 +3567,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3692,6 +3717,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6028,6 +6058,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6173,6 +6208,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6318,6 +6358,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9053,6 +9098,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9198,6 +9248,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9343,6 +9398,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11679,6 +11739,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11824,6 +11889,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11969,6 +12039,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14852,6 +14927,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15387,6 +15467,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15532,6 +15617,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17856,6 +17946,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18781,6 +18876,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18926,6 +19026,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21395,6 +21500,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21930,6 +22040,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22075,6 +22190,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24940,6 +25060,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26810,118 +26935,522 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AT150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN151" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP151" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AT151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV151" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
+      <c r="G152" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>D049</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>MERS</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
         <is>
           <t>中东呼吸综合征</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
+      <c r="K152" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
+      <c r="L152" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M150" t="inlineStr">
+      <c r="M152" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N150" t="n">
-        <v>0</v>
-      </c>
-      <c r="O150" t="n">
-        <v>0</v>
-      </c>
-      <c r="R150" t="n">
-        <v>0</v>
-      </c>
-      <c r="S150" t="inlineStr">
+      <c r="N152" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0</v>
+      </c>
+      <c r="S152" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO150" t="inlineStr">
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP150" t="inlineStr">
+      <c r="AP152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR150" t="inlineStr">
+      <c r="AR152" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS150" t="inlineStr"/>
-      <c r="AT150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU150" t="inlineStr">
+      <c r="AS152" t="inlineStr"/>
+      <c r="AT152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU152" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV150" t="inlineStr">
+      <c r="AV152" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW150" t="inlineStr">
+      <c r="AW152" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX150" t="inlineStr">
+      <c r="AX152" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY150" t="inlineStr">
+      <c r="AY152" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ150" t="inlineStr">
+      <c r="AZ152" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA150" t="inlineStr">
+      <c r="BA152" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB150" t="inlineStr">
+      <c r="BB152" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC150" t="inlineStr">
+      <c r="BC152" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -27043,7 +27572,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10">
@@ -27053,7 +27582,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11">
@@ -27073,7 +27602,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d049/2026-2029.xlsx
+++ b/diseases/d049/2026-2029.xlsx
@@ -27456,6 +27456,151 @@
         </is>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr"/>
+      <c r="AT153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27489,7 +27634,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -27572,7 +27717,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10">
@@ -27582,7 +27727,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d049/2026-2029.xlsx
+++ b/diseases/d049/2026-2029.xlsx
@@ -27601,6 +27601,405 @@
         </is>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AT154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA154" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB154" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC154" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>mers</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>Middle East Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN155" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MIDDLE_EAST_RESPIRATORY_SYNDROME</t>
+        </is>
+      </c>
+      <c r="AT155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27717,7 +28116,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10">
@@ -27727,7 +28126,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -27747,7 +28146,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
